--- a/Расписание/2026_ОСЕНЬ_ЗИМА_Расписание.xlsx
+++ b/Расписание/2026_ОСЕНЬ_ЗИМА_Расписание.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gamedev\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\rabota\Расписание\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D049F3-5ADF-4706-87A8-CC27F03E43F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DB8A87-C86D-4DF3-B72A-DA83654D4094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>пн</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>5vr (прод)</t>
+  </si>
+  <si>
+    <t>Время</t>
   </si>
 </sst>
 </file>
@@ -83,13 +86,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,12 +107,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -141,6 +138,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -220,34 +229,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -528,10 +548,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D2:I7"/>
+  <dimension ref="C2:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" customWidth="1"/>
     <col min="6" max="6" width="28.140625" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -539,78 +560,85 @@
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="10"/>
+    <row r="2" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="16"/>
       <c r="E3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="6" t="s">
+    <row r="4" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="18"/>
+      <c r="E4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="7" t="s">
+    <row r="5" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="19"/>
+      <c r="E5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="8" t="s">
+    <row r="6" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="D6" s="20"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="9" t="s">
+    <row r="7" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="21"/>
+      <c r="E7" s="17" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="3"/>
@@ -620,5 +648,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>